--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/phi-4/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/phi-4/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="D3">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>426</v>
